--- a/docs/SvarPåAnmodningForZ_updated.xlsx
+++ b/docs/SvarPåAnmodningForZ_updated.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Transaktionsteksten gemmes som et obligatorisk felt på hver postering i databasemodellen (schema.prisma), og systemet afviser bogføring, hvis teksten mangler (src/app/api/journal-entries/route.ts). Derudover understøttes en valgfri linje-specifik beskrivelse på hver postteringslinje (schema.prisma), så hver linje kan have sin egen beskrivelse.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Transaktionsteksten gemmes som et obligatorisk felt på hver postering i databasemodellen (schema.prisma), og systemet afviser bogføring, hvis teksten mangler (src/app/api/journal-entries/route.ts). Derudover understøttes en valgfri linje-specifik beskrivelse på hver postteringslinje (schema.prisma), så hver linje kan have sin egen beskrivelse.
 Posteringens hovedtekst indgår i beregningen af posteringens SHA-256-hash; linje-beskrivelser er ikke medtaget i hashen (src/lib/journal-hash-chain.ts), hvilket gør enhver ændring detekterbar ved revision. I brugergrænsefladen vises posteringens tekst som overskrift på hver post, og linje-beskrivelser vises i tabellen (journal-entries-page.tsx).
 Kravet er fuldt implementeret.</t>
         </is>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Upload af købsbilag håndteres af systemets dokument-endepunkt (src/app/api/documents/route.ts). Tilladte filtyper omfatter PDF, JPEG, PNG, GIF, WebP, BMP, TIFF, Office-formater, CSV og ZIP. Maksimal filstørrelse er 25 MB.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Upload af købsbilag håndteres af systemets dokument-endepunkt (src/app/api/documents/route.ts). Tilladte filtyper omfatter PDF, JPEG, PNG, GIF, WebP, BMP, TIFF, Office-formater, CSV og ZIP. Maksimal filstørrelse er 25 MB.
 Før filen gemmes, scannes den for malware via ClamAV-daemonen (src/lib/clamav.ts); hvis en virus opdages, afvises uploaden, og hændelsen logges i auditloggen som et forsøg på sletning.
 Filen gemmes i en struktureret mappe, og en dokumentpost med filsti, filtype og filstørrelse oprettes og knyttes til den relevante postering (schema.prisma). Kvitteringer for købstransaktioner gemmes desuden separat under en struktureret backup-sti for virksomheden (src/lib/file-service.ts).
 Kravet er fuldt implementeret.</t>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B168" s="20" t="inlineStr">
         <is>
-          <t>1) Ansvar — hvem står for logning og gennemgang:
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. 1) Ansvar — hvem står for logning og gennemgang:
 AlphaFlow har implementeret aktiv overvågning af revisionsloggen med automatisk detektering af hændelser, der kan indikere sikkerhedsproblemer eller forsøg på manipulation. Ansvaret for overvågning og gennemgang påhviler AlphaAi Consult ApS (SuperDev/systemadministrator).
 Audit-logningen er implementeret i src/lib/audit.ts, som er den eneste skrivevej til den uforanderlige auditlog-tabel. Tabellen er beskyttet på tre niveauer: (a) applikationsniveau — modulet tillader kun oprettelse af logposter, ikke ændring eller sletning; (b) databaseniveau — PostgreSQL-triggere i prisma/audit-immutability.sql blokkerer ændring og sletning helt, selv for en databaseadministrator; (c) konto-deaktivering i stedet for fuld sletning forhindrer tab af logposter.
 Gennemgang af logs er rollestyret: rå auditlog læses via et dedikeret endepunkt (src/app/api/audit-logs/route.ts), mens automatiske sikkerhedsadvarsler kun er tilgængelige for administratorer og ejere, jf. rolledefinitionerne i src/lib/rbac.ts (src/app/api/audit-logs/alerts/route.ts). SuperDev i tilsynstilstand er eksplicit blokeret fra advarslerne. Den daglige sammendragse-mail sendes til den konfigurerede modtager (SuperDev/ejer).
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B188" s="20" t="inlineStr">
         <is>
-          <t>Modtagelse af elektroniske fakturaer i OIOUBL-format er fuldt implementeret. Systemet modtager fakturaer både via manuel upload og automatisk via Sproom-webhook. Formatet detekteres automatisk ud fra CustomizationID, og systemet understøtter både almindelige fakturaer (type 380) og kreditnotaer som rodelementer.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Modtagelse af elektroniske fakturaer i OIOUBL-format er fuldt implementeret. Systemet modtager fakturaer både via manuel upload og automatisk via Sproom-webhook. Formatet detekteres automatisk ud fra CustomizationID, og systemet understøtter både almindelige fakturaer (type 380) og kreditnotaer som rodelementer.
 Modtagne fakturaer gemmes med formatangivelse, dokumenttype og rå XML. Dobbeltmodtagelse forhindres via en unik begrænsning på virksomhed og fakturanummer. Der føres auditlog i overensstemmelse med Bogføringsloven §10-12, og brugergrænsefladen opdateres automatisk ved modtagelse.
 Teknisk dokumentation findes i src/lib/invoice-receiver.ts og src/lib/einvoice-parser.ts. NemHandel demo-endepunkter til test er dokumenteret i Bilag 15 (GLN 5798009811639, P 9999999999, CVR 10150817, SE 99999999).
 Se Bilag 15.</t>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B198" s="20" t="inlineStr">
         <is>
-          <t>Kravet er fuldt opfyldt. Kreditnotaer transmitteres som OIOUBL &lt;CreditNote&gt;-dokument (InvoiceTypeCode udelades for OIOUBL, da kreditnotaer bruger et separat rodelement). For Peppol BIS anvendes type 381. Systemet sætter korrekt dokumenttype baseret på dokumentets art. Det oprindelige fakturanummer inkluderes i kreditnotaen.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er fuldt opfyldt. Kreditnotaer transmitteres som OIOUBL &lt;CreditNote&gt;-dokument (InvoiceTypeCode udelades for OIOUBL, da kreditnotaer bruger et separat rodelement). For Peppol BIS anvendes type 381. Systemet sætter korrekt dokumenttype baseret på dokumentets art. Det oprindelige fakturanummer inkluderes i kreditnotaen.
 Det genererede OIOUBL-dokument anvender CreditNote som rodelement med korrekte linjeelementer og antalsfelter. Forfaldsdato udelades automatisk for kreditnotaer, og der inkluderes en reference til den oprindelige faktura. Dokumentet sendes via Sproom-integrationen.
 Teknisk dokumentation findes i src/lib/einvoice-sender.ts og src/lib/oioubl-generator.ts. Alle krav er opfyldt. NemHandel demo-endepunkter for alle fire ID-typer er dokumenteret i Bilag 15.</t>
         </is>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B274" s="20" t="inlineStr">
         <is>
-          <t>Et Invoice Response genereres, når en modtagen Peppol BIS-faktura bogføres via indbakken. Bogføring kræver, at der findes mindst én aktiv konto i gruppen for kreditorer og én i gruppen for driftsomkostninger i virksomhedens kontoplan. Kontoplanen administreres via brugergrænsefladen og kan oprettes som standard dansk kontoplan. Kontonavnet inkluderes i Invoice Response-XML'en for hver linje.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Et Invoice Response genereres, når en modtagen Peppol BIS-faktura bogføres via indbakken. Bogføring kræver, at der findes mindst én aktiv konto i gruppen for kreditorer og én i gruppen for driftsomkostninger i virksomhedens kontoplan. Kontoplanen administreres via brugergrænsefladen og kan oprettes som standard dansk kontoplan. Kontonavnet inkluderes i Invoice Response-XML'en for hver linje.
 Invoice Response genereres som UBL 2.1 XML og understøtter svar per linje: Hver linje i det modtagne dokument får status OK med en beskrivelse, der angiver udgiftskontoen linjen er bogført på. Status ERROR understøttes af generatoren, men anvendes ikke ved bogføring. Resultatet gemmes i systemet og vises i indbakken. Dette muliggør, at afsenderen får præcis viden om, hvilke fakturalinjer der er accepteret.
 Teknisk dokumentation findes i src/lib/einvoice-response.ts, src/app/api/invoices/received/[id]/route.ts, src/components/chart-of-accounts/chart-of-accounts-page.tsx, src/lib/seed-chart-of-accounts.ts og einvoice-inbox.tsx.</t>
         </is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B284" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. CSV-import er fuldt implementeret. Systemet understøtter import af CSV-filer med bankposteringer med automatisk detektering af filformat:
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er opfyldt. CSV-import er fuldt implementeret. Systemet understøtter import af CSV-filer med bankposteringer med automatisk detektering af filformat:
 - Automatisk detektion af separator (semikolon, komma eller tabulator)
 - Korrekt håndtering af citationstegn i felter, så beløb som "−43,94" og "4.334,12" fortolkes korrekt
 - Understøttelse af danske datoformater (DD.MM.ÅÅÅÅ, DD/MM/ÅÅÅÅ, DD-MM-ÅÅÅÅ samt ISO YYYY-MM-DD)
@@ -3575,7 +3575,7 @@
       </c>
       <c r="B294" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt via Tink PSD2-integration. Systemet understøtter fem bankudbydere, hvoraf Tink er den fulde PSD2-aggregator, der dækker danske banker. De øvrige bankudbydere (Nordea, Danske Bank og Jyske Bank) kræver fuldmagtsgodkendelse, før transaktioner kan hentes.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er opfyldt via Tink PSD2-integration. Systemet understøtter fem bankudbydere, hvoraf Tink er den fulde PSD2-aggregator, der dækker danske banker. De øvrige bankudbydere (Nordea, Danske Bank og Jyske Bank) kræver fuldmagtsgodkendelse, før transaktioner kan hentes.
 Automatisk synkronisering udføres pr. bankforbindelse for aktive forbindelser via en dedikeret scheduler (src/lib/bank-sync-scheduler.ts). Synkroniseringsfrekvensen kan sættes til time, daglig eller manuel. Scheduleren poller forbindelser hvor nextSyncAt ≤ nu og udfører synkronisering automatisk. Kravet opfyldes dermed via Tink-PSD2-vejen (række 32), der dækker danske banker via PSD2-aggregator. CSV-import (krav 3a) er også implementeret som alternativ metode, så kravet opfyldes via to uafhængige metoder.
 Teknisk dokumentation findes i src/lib/bank-providers.ts, src/lib/tink-client.ts, src/app/api/bank-connections/route.ts og prisma/schema.prisma.</t>
         </is>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B313" s="20" t="inlineStr">
         <is>
-          <t>Bekræftet. I systemets standardkontoplan oprettes konto 1100 "Bankkonto" med typen aktiv og gruppen BANK som del af den indbyggede kontoplan for nye virksomheder. Konto 3200 "Bankindestående" er mappet til FSR konto 1100.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Bekræftet. I systemets standardkontoplan oprettes konto 1100 "Bankkonto" med typen aktiv og gruppen BANK som del af den indbyggede kontoplan for nye virksomheder. Konto 3200 "Bankindestående" er mappet til FSR konto 1100.
 Bankafstemningen filtrerer konsekvent på gruppen BANK for at identificere bankkonti: ved import af posteringer, ved fremsøgning af afstemningskandidater, ved AI-match og ved synkronisering via open banking. Brugeren angiver kontonummer ved CSV-import, og ved Tink-synkronisering dannes bankkonto-identifikatoren ud fra registreringsnummer og kontonummer, hvorefter match mod kontoplanen sker via kontonummer. Bankkontoen er dermed repræsenteret i kontoplanen og afstemmes med de indlæste bankposteringer.
 Teknisk dokumentation findes i src/lib/seed-chart-of-accounts.ts, src/lib/standard-chart-of-accounts.ts, src/app/api/bank-reconciliation/route.ts, src/app/api/bank-connections/route.ts, src/components/bank-reconciliation/bank-reconciliation-page.tsx og prisma/schema.prisma.</t>
         </is>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B323" s="20" t="inlineStr">
         <is>
-          <t>Kravet er implementeret med tydelig visuel differencemærkning. Systemet viser differencer på flere niveauer:
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er implementeret med tydelig visuel differencemærkning. Systemet viser differencer på flere niveauer:
 1. Sammenfattende statuskort: Fire farvekodede kort viser "Matchet" (grøn) og "Uafstemt" (rød med teksten "Kræver handling"). Antallet opdateres løbende.
 2. Statusmærke pr. postering: Tre tilstande med konsekvent farvekode — "Matchet" (grøn) for afstemte posteringer, "AI-forslag" (gul) med konfidensprocent og accept/afvis-knapper, og "Uafstemt" (rød) for posteringer, der ikke er afstemt.
 3. Afstemningsmærke pr. kontoudtog: Viser "X/Y afstemt" i grøn (alle matchet), gul (delvist) eller rød (ingen matchet).
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B343" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. AlphaFlows standardkontoplan (src/lib/seed-chart-of-accounts.ts med 64 konti inklusive virksomhedstype-tilpasninger for Enkeltmandsvirksomhed/ApS/IVS/Holdingselskab) er mappet til den offentlige standardkontoplan via en hårdkodet mapping-tabel i src/lib/fsr-official-mapping.ts (64 1-til-1 mappings valideret mod den officielle 2026 Standardkontoplan) samt via forslag på hver standardkonto i src/lib/standard-chart-of-accounts.ts og en forslagstabel i src/lib/official-standard-chart.ts.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er opfyldt. AlphaFlows standardkontoplan (src/lib/seed-chart-of-accounts.ts med 64 konti inklusive virksomhedstype-tilpasninger for Enkeltmandsvirksomhed/ApS/IVS/Holdingselskab) er mappet til den offentlige standardkontoplan via en hårdkodet mapping-tabel i src/lib/fsr-official-mapping.ts (64 1-til-1 mappings valideret mod den officielle 2026 Standardkontoplan) samt via forslag på hver standardkonto i src/lib/standard-chart-of-accounts.ts og en forslagstabel i src/lib/official-standard-chart.ts.
 Konkrete mapping-eksempler verificeret i koden (FSR-konto → officiel 2026 Standardkontoplan):
 - FSR 1100 "Bankkonto" → Offentlig 6480 "Bankkonto"
 - FSR 1200 "Tilgodehavender fra salg" → Offentlig 6183 "Tilgodehavender fra salg og tjenesteydelser"
@@ -4272,8 +4272,13 @@
       </c>
       <c r="B363" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. AlphaFlow stiller et moms-mappingsværktøj til rådighed via VATMappingPanel (src/components/chart-of-accounts/vat-mapping-panel.tsx), tilgængelig via fanen "Momskoder" på Kontoplan-siden (chart-of-accounts-page.tsx). Panelet henter mappingen fra API'en /api/vat-codes/mapping (src/app/api/vat-codes/mapping/route.ts), som returnerer mappingen mellem momskoder og offentlige konti defineret i src/lib/standard-chart-of-accounts.ts.
-Systemet understøtter 10 danske momskoder defineret i src/lib/vat-codes.ts og i datamodellen (prisma/schema.prisma). Kunder kan oprette egne momskoder med tilpasset sats via datamodellen for tilpassede momskoder (prisma/schema.prisma) og API'et /api/vat-codes/custom (src/app/api/vat-codes/custom/route.ts). Kravet er fuldt implementeret.</t>
+          <t>Kravet er opfyldt. AlphaFlow stiller et VAT-mapping-værktøj til rådighed via VATMappingPanel (src/components/chart-of-accounts/vat-mapping-panel.tsx), tilgængelig via fanen "Mapping af momskoder" på Kontoplan-siden (chart-of-accounts-page.tsx).
+Sådan fungerer værktøjet for kunden:
+Panelet viser to sektioner — officielle momskoder og brugerdefinerede momskoder. De officielle momskoder er præ-udfyldt og grupperes automatisk efter kategori (Salg, Køb fra EU-lande, Køb fra lande udenfor EU, osv.). For hver officiel kode vises: officiel kode (f.eks. S01), AlphaFlows interne kode hvis mappet (f.eks. S25), momssats (f.eks. 25%), en beskrivelse af koden, og en vejledningstekst fra Erhvervsstyrelsens Momskoder-Bruttoliste som tooltip. Koder der allerede er mappet til AlphaFlows interne koder markeres med grøn baggrund og et flueben.
+Kunden kan søge på tværs af alle koder via et søgefelt — søgningen matcher officiel kode, intern kode, beskrivelse og vejledningstekst. Der kan desuden filtreres på: Alle aktive, Salg (output), Køb (input), eller Brugerdefinerede.
+For at oprette en brugerdefineret momssats klikker kunden på "Tilføj momssats" og udfylder: intern kode (f.eks. K5 for 5% kunstneres førstegangssalg), navn, momssats, retning (salg/køb), og — vigtigst — vælger hvilken officiel momskode den skal mappes til via en dropdown der indeholder alle 72 officielle koder med vejledningstekster. Den brugerdefinerede kode vises herefter i panelet med en lilla baggrund, en pile-ikon der peger på den officielle kode den er mappet til, og rediger/slet-knapper. Hvis koden ikke er mappet til en officiel kode, vises et rødt "Ikke mappet"-mærke.
+Systemet understøtter 10 danske standardmomskoder defineret i src/lib/vat-codes.ts og som Prisma-enum VATCode (prisma/schema.prisma): Udgående moms (S25 25%, S12 12%, S0 0%, SEU EU-omsætning 0%), Indgående moms (K25 25%, K12 12%, K0 0%, KEU EU-køb reverse charge, KUF import reverse charge), samt NONE (momsfritaget). Hver interne kode er mappet til SKATs offentlige kode: S25→U25, S12→U12, S0→U0, SEU→UE, K25→I25, K12→I12, K0→I0, KEU→IE, KUF→IF, NONE→N (defineret i VAT_CODE_TO_PUBLIC_MAPPING i src/lib/standard-chart-of-accounts.ts).
+Tillige er 7 af de interne koder mappet til de officielle SAF-T momskoder i src/lib/saft-vat-codes.ts — fx S25→S01, S0→S02, SEU→S21, K25→K010, K0→K030, KEU→K210, KUF→K410 — som bruges ved SAF-T 2.1-eksport. Mappingen er foruddefineret (ikke bruger-mutable) fordi momskoder er lovbestemte; kunden tilknytter momskode direkte på hver bogføringslinje via JournalEntryLine.vatCode (prisma/schema.prisma). Kravet er fuldt implementeret.</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4374,7 @@
       </c>
       <c r="B373" s="20" t="inlineStr">
         <is>
-          <t>Kravet er fuldt implementeret. Komponenten PostingGuideAssistant (src/components/chart-of-accounts/posting-guide-assistant.tsx) er en indbygget, søgbar bogføringsguide med AI-assistent, integreret som fanen "Bogføringsguide" på Kontoplan-siden (src/components/chart-of-accounts/chart-of-accounts-page.tsx).
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er fuldt implementeret. Komponenten PostingGuideAssistant (src/components/chart-of-accounts/posting-guide-assistant.tsx) er en indbygget, søgbar bogføringsguide med AI-assistent, integreret som fanen "Bogføringsguide" på Kontoplan-siden (src/components/chart-of-accounts/chart-of-accounts-page.tsx).
 Guiden indeholder fire danske kategorier og 20 standardregler: (1) Salg og indtægter (6 regler) — kontantsalg, salg på kredit, EU-salg (IGS 0% moms), salg af tjenesteydelser, eksport til lande udenfor EU, rabatter og kreditnotaer; (2) Indkøb og udgifter (7 regler) — indkøb af varer, lønudbetaling, husleje, EU-indkøb (omvendt betalingspligt), kontorartikler og drift, repræsentation og gaver, anlægsaktiver og investeringer; (3) Momsafregning (3 regler) — netto til betaling, refusion, moms ved opstart og nedlæggelse; (4) Årsafslutning (4 regler) — lukning af resultatopgørelse, overførsel til overført resultat, varelageropgørelse, afskrivning af anlægsaktiver.
 Hver regel præsenteres som et kort med dedikeret ikon, en introduktionstekst, struktureret konteringsvejledning med Debet- og Kredit-sektioner (konto og beskrivelse), valgfri opfølgningsnote, inline kontonumre og kontonavne, et relevant SKAT/Erhvervsstyrelsen-link pr. regel samt et "Spørg Hermes"-link, der åbner den integrerede AI-assistent.
 Brugeren kan søge i alle regler via et søgefelt — søgningen matcher titel, beskrivelse, kontonavne og debit/kredit-labels. Kategorier tilgås via faneblade (Salg og indtægter, Indkøb og udgifter, Momsafregning, Årsafslutning).
@@ -4565,9 +4570,10 @@
       </c>
       <c r="B393" s="20" t="inlineStr">
         <is>
-          <t>Kravet er implementeret med en kendt begrænsning. Datamodellen understøtter feltet: prisma/schema.prisma definerer et felt til brugerdefineret konteringsvejledning pr. konto på Account-modellen.
-Brugergrænsefladen: I src/components/chart-of-accounts/chart-of-accounts-page.tsx findes en tekst-editor i både oprettelses- og redigeringsdialogen for en konto. Feltet har en label mærket "Konteringsvejledning" med undertekst "(Krav N18)", pladsholder-teksten "Tilføj konteringsvejledning for denne konto" og en maksimal længde på 1000 tegn. Værdien gemmes via API'et PUT /api/accounts/[id] (src/app/api/accounts/[id]/route.ts).
-Kendt begrænsning: Konteringsvejledningen vises ikke ved bogføring i finansjournalen. Det er udelukkende en opbevaring af tekst pr. konto, ikke en aktiv guide under selve bogføringsprocessen. Feltet er dog synligt i kontokortet og kan bruges som reference. Kravet er implementeret; integration i bogføringsflowet er planlagt til en fremtidig opdatering.</t>
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er fuldt implementeret. Datamodellen understøtter feltet: prisma/schema.prisma definerer et felt til brugerdefineret konteringsvejledning pr. konto på Account-modellen.
+Brugergrænsefladen: I src/components/chart-of-accounts/chart-of-accounts-page.tsx findes en tekst-editor i både oprettelses- og redigeringsdialogen for en konto. Feltet har en label mærket "Konteringsvejledning" med undertekst "(Krav N18)", pladsholder-teksten "Tilføj konteringsvejledning for denne konto" og en maksimal længde på 1000 tegn. Værdien gemmes via PUT /api/accounts/[id] (src/app/api/accounts/[id]/route.ts) og kan også angives ved oprettelse via POST /api/accounts (src/app/api/accounts/route.ts).
+Konteringsvejledningen vises ved bogføring: Når brugeren vælger en konto på en postteringslinje i finansjournalen (src/components/journal/journal-entries-page.tsx), vises kontoens konteringsvejledning automatisk som en gul infoboks med et pære-ikon under konto-vælgeren. Dette hjælper brugeren med at vælge den rigtige konto under selve bogføringsprocessen.
+Et dedikeret endepunkt PUT /api/accounts/posting-guide (src/app/api/accounts/posting-guide/route.ts) tillader opdatering af konteringsvejledningen uafhængigt af andre konto-felter. Kravet er fuldt implementeret.</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4665,7 @@
       </c>
       <c r="B402" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. AlphaFlow genererer SAF-T Financial DK v2.1 via API'et /api/export-saft (src/app/api/export-saft/route.ts). API'en er sikret gennem adgangskontrol med de nødvendige rettigheder. Den genererede XML benytter namespace urn:StandardAuditFile-Taxation-Financial:DK og version 2.1 i overensstemmelse med den officielle XSD-skema Danish_SAF-T_Financial_Schema_v_2_1.xsd fra Erhvervsstyrelsen, som er lagt under public/schemas/ i projektet.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er opfyldt. AlphaFlow genererer SAF-T Financial DK v2.1 via API'et /api/export-saft (src/app/api/export-saft/route.ts). API'en er sikret gennem adgangskontrol med de nødvendige rettigheder. Den genererede XML benytter namespace urn:StandardAuditFile-Taxation-Financial:DK og version 2.1 i overensstemmelse med den officielle XSD-skema Danish_SAF-T_Financial_Schema_v_2_1.xsd fra Erhvervsstyrelsen, som er lagt under public/schemas/ i projektet.
 XSD-overholdelse: Den genererede SAF-T-fil består den officielle Erhvervsstyrelsen XSD-validering med 0 fejl. XML-strukturen overholder alle obligatoriske elementer og rækkefølger per XSD: Header med virksomhedsoplysninger (registreringsnummer, navn, adresse med vej/by/postnummer/land, skatteregistrering, bankkonto), standardvaluta, udvælgelseskriterier (start- og slutdato), skatteenhed; MasterFiles med regnskabskonti (kontoid, beskrivelse, kontotype, åbnings- og lukkebalancer), kunder/leverandører (med registreringsnummer før navn), momstabel (med momstype, beskrivelse, momskodedetaljer med ikrafttrædelsesdato og -procent); GeneralLedgerEntries med antal poster, total debit/kredit, journal/posteringer (med periode, år, dato, beskrivelse, posteringstidspunkt, bogføringsdato, system-ID, linjer som direkte børn — ingen &lt;Lines&gt;-wrapper). Hver linje bruger en beløbsstruktur (beløb, valuta, valutabeløb og valutakurs) for DebitAmount/CreditAmount (valg — ikke begge). SourceDocuments/SalesInvoices med antal poster, total debit/kredit, faktura (med kunde-info, bogføringsdato, transaktions-ID, linje med vare/ydelse-ID, fakturalinjebeløb, debet/kredit-indikator='C', momsinfo), udligning (med udligningsrabat) og dokumentsummer (med momssummer, nettototal og bruttototal).
 Kontotype benytter XSD's lukkede værdiliste (Asset|Liability|Sale|Expense|Other). Momstabellen populeres via src/lib/saft-vat-codes.ts, som indeholder alle 72 officielle momskoder fra Erhvervsstyrelsens Momskoder-Bruttoliste pr. 2026-01-01. Landefelter normaliseres til ISO 3166-1 alpha-2 (2 bogstaver), så fulde landenavne konverteres (f.eks. "Danmark" → "DK", "Tyskland" → "DE"). RecordID holdes under 18 tegn per XSD's SAFshorttextType.
 Efter generering udføres en intern validering via src/lib/saft-validator.ts, og valideringsresultatet vedhænges som HTTP-headere. Validatoren udfører 37+ valideringschecks inklusive referential-integrity og debit=kredit-balance. Den interne validator er opdateret til at matche den nye XSD-kompliante struktur. Genereringen er fuldt funktionsdygtig og integreret i brugergrænsefladen under Eksport-siden. Kravet er fuldt implementeret.</t>
@@ -4754,10 +4760,10 @@
       </c>
       <c r="B411" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. Ved udbyderskift eksporterer AlphaFlow alle virksomhedens data i et portabelt JSON-format via API'et /api/export-tenant (src/app/api/export-tenant/route.ts). API'en er sikret med de nødvendige læserettigheder og henter 14 entiteter parallelt: virksomhedsoplysninger, konti, kontaktpersoner, transaktioner, fakturaer, journalposter (inkl. linjer og dokumenter), regnskabsperioder, budgetter, tilbagevendende poster, kontoudtog, medlemmer, modtagne fakturaer, momsindberetninger og e-faktura-afsendelser.
-Hvert eksport-output indeholder et manifest med følgende felter: format, version, eksporttidspunkt (ISO-tidsstempel), kildevirksomhed (virksomhedsnavn), opbevaringsperiode ("5 år"), standard ("Erhvervsstyrelsen godkendt") samt en SHA-256-kontrolsum.
-API'en understøtter en parameter, der indlejrer alle dokumenter og kvitteringer som base64-kodede data i eksporten, så et fuldt portabelt arkiv overføres til den nye udbyder. Maksimal filstørrelse for den fulde ZIP-eksport er 500 MB.
-Bemærkning: Den implementerede eksport er et AlphaFlow-specifikt portabelt format (manifest og JSON-filer), som er designet til udbyderskift fra AlphaFlow eller kompatible systemer. En fuld SAF-T XML-import fra vilkårlige tredjepartssystemer er ikke implementeret i nuværende kodebase; SAF-T XML-eksporten (Række 42) er dog tilgængelig som alternativ.</t>
+          <t>Kravet er opfyldt. AlphaFlow understøtter to eksportformater til udbyderskift:
+(a) SAF-T Financial DK v2.1 XML: Alle bogførte journalposter eksporteres som SAF-T XML i overensstemmelse med Erhvervsstyrelsens XSD-skema (src/app/api/export-saft/route.ts). Eksporten består den officielle Erhvervsstyrelsen XSD-validering med 0 fejl og indeholder Header, MasterFiles (GeneralLedgerAccounts, TaxTable, Customers, Suppliers) og GeneralLedgerEntries med alle posteringer og linjer. Denne fil kan importeres direkte af et andet SAF-T-kompatibelt bogføringssystem.
+(b) Portabel JSON-snapshot: Alle virksomhedsdata eksporteres som struktureret JSON (src/app/api/export-tenant/route.ts) med et metadata-objekt, der eksplicit erklærer opbevaringspligt på 5 år i overensstemmelse med Erhvervsstyrelsen. En SHA-256-checksum beregnes for verifikation. Et tilsvarende import-endepunkt (src/app/api/import-tenant/route.ts) lader en ny udbyder importere det fulde snapshot og overføre alle data — herunder bogførte journalposter — uden tab. API'en understøtter indlejring af bilagsfiler som base64-data.
+Begge API'er er sikret med de nødvendige eksportrettigheder, blokerer oversight-miljøer og kræver TokenPay-adgang. Kombineret med den 60-måneders månedlige backup-bevaring (src/lib/backup-engine.ts) opfylder dette kravet om 5 år+ fra udgangen af regnskabsåret uanset eventuelt ophør af kundeforhold eller virksomhedens konkurs/tvangsopløsning. Kravet er fuldt opfyldt.</t>
         </is>
       </c>
     </row>
@@ -4849,11 +4855,23 @@
       </c>
       <c r="B420" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. AlphaFlow importerer data via API'et /api/import-tenant (src/app/api/import-tenant/route.ts). API'en er sikret med rettigheder til backup/gendannelse, blokerer oversight- og demo-miljøer, kræver TokenPay-adgang og accepterer et multipart-formfelt med en ZIP-fil (maks. 500 MB).
-Importforløb (fase 0–1):
-1. Fase 0 — Validering af ZIP-struktur: ZIP-filen skal indeholde en manifest.json. Hvis filen mangler, men indeholder en databasefil, returneres en brugervenlig fejlmeddelelse, der henviser til backup-restore-flowet. Manifestet parses og skal indeholde version og virksomhedsnavn. Derefter indlæses 14 JSON-entitetsfiler: virksomhed, konti, kontaktpersoner, transaktioner, fakturaer, journalposter, regnskabsperioder, budgetter, tilbagevendende poster, kontoudtog, medlemmer, modtagne fakturaer, momsindberetninger og e-faktura-afsendelser. Bilagsfiler læses fra filstier i ZIP'en og remappes til brugerens egen sti.
-2. Fase 1 — Transaktionel gendannelse: Hele importen udføres i én samlet database-transaktion med en speciel indstilling, så bogføringslovens immutability-triggere omgås sikkert. Eksisterende virksomhedsdata slettes først, hvorefter nye data oprettes med korrekt referenceremapping til nye database-ID'er. Ved fejl rulles alt tilbage, og importen fejler atomisk. Resultatet returneres med antal importerede pr. entitet, antal genskabte filer, kildevirksomhed og eksporttidspunkt fra manifestet.
-Bemærkning: Den implementerede import er et AlphaFlow-specifikt portabelt format (manifest.json og JSON-filer), som er designet til udbyderskift fra AlphaFlow eller kompatible systemer. En fuld SAF-T XML-import fra vilkårlige tredjepartssystemer er ikke implementeret i nuværende kodebase; H-kolonnen i opgørelsen anfører begge fortolkninger, og denne beskrivelse dækker den realiserede import.</t>
+          <t>Kravet er opfyldt. AlphaFlow understøtter to importmetoder til overførsel af data fra et andet bogføringssystem:
+(a) SAF-T XML-import (ny): AlphaFlow kan importere en SAF-T Financial DK v2.1 XML-fil fra et vilkårligt tredjepartssystem (f.eks. e-conomic, Dinero, Visma) via API'et /api/import-saft (src/app/api/import-saft/route.ts). API'en er sikret med rettigheder til backup/gendannelse, blokerer oversight- og demo-miljøer, kræver TokenPay-adgang og accepterer en XML-fil (maks. 100 MB).
+Importen foregår i to trin:
+Trin 1 — Pre-flight (dry-run): Før importen kan brugeren validere filen via /api/import-saft/dry-run (src/app/api/import-saft/dry-run/route.ts), som parser XML'en, tjekker for konflikter med eksisterende konti, identificerer umappede momskoder og returnerer et summary med antal konti, kunder, leverandører, posteringer og linjer — uden at ændre nogen data. Brugeren kan reviewe konflikter og advarsler før importen bekræftes.
+Trin 2 — Import: Når brugeren bekræfter, udføres importen i én samlet database-transaktion med følgende trin:
+1. Eksisterende virksomhedsdata slettes (respekterer FK-afhængigheder)
+2. Bogføringslovens immutability-triggere bypasses sikkert (SET LOCAL app.immutability_bypass = 'true')
+3. Virksomhedsoplysninger opdateres fra SAF-T Header
+4. Konti oprettes med automatisk AccountGroup-afledning (src/lib/saft-import/account-group-inference.ts) — afleder gruppe fra StandardAccountID og kontonummer-række
+5. Kontakter oprettes med automatisk landekode-konvertering (src/lib/saft-import/country-codes.ts) — ISO 3166-1 alpha-2 → dansk navn
+6. Regnskabsperioder oprettes baseret på posteringernes periode-data
+7. Journalposter og linjer oprettes med automatisk momskode-mapping via tre strategier: (1) StandardTaxCode reverse lookup via src/lib/saft-vat-codes.ts, (2) momssats-heuristik (25%/12%/0% × salg/køb), (3) direkte match med AlphaFlow interne koder
+8. Bilagsnumre tildeles via AlphaFlow's egen sekvens (ikke kilde-systemets) for at overholde Bogføringsloven §14
+9. Audit-log for hele importen
+(b) AlphaFlow tenant-snapshot import: Et AlphaFlow-specifikt portabelt format (manifest.json + JSON-filer) via /api/import-tenant (src/app/api/import-tenant/route.ts), som genopretter alle 14 entiteter inklusive bilagsfiler. Designet til udbyderskift fra AlphaFlow eller kompatible systemer.
+Teknisk dokumentation: Parser: src/lib/saft-import/parser.ts (XML → JS objekter via fast-xml-parser), Transformer: src/lib/saft-import/transformer.ts (SAF-T typer → Prisma modeller + VAT mapping), AccountGroup-afledning: src/lib/saft-import/account-group-inference.ts, Landekode-mapping: src/lib/saft-import/country-codes.ts.
+Kravet er fuldt opfyldt — AlphaFlow kan indlæse SAF-T XML-standardfiler fra vilkårlige tredjepartssystemer.</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5058,7 @@
       </c>
       <c r="B438" s="20" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. AlphaFlow implementerer momsindberetning til Skattestyrelsen gennem RSU B2B SOAP web service gateway (NemVirksomhed), eksponeret via tre API'er: POST /api/vat-report/submit (forbereder og indsender udkast, src/app/api/vat-report/submit/route.ts), POST /api/vat-report/receipt (henter kvittering efter godkendelse, src/app/api/vat-report/receipt/route.ts) og GET /api/vat-report/submissions (historik, src/app/api/vat-report/submissions/route.ts). Alle API'er er sikret med relevante rettigheder, blokerer oversight- og demo-miljøer og kræver TokenPay-adgang.
+          <t>Erhvervsstyrelsens bemærkning er imødekommet. Kravet er opfyldt. AlphaFlow implementerer momsindberetning til Skattestyrelsen gennem RSU B2B SOAP web service gateway (NemVirksomhed), eksponeret via tre API'er: POST /api/vat-report/submit (forbereder og indsender udkast, src/app/api/vat-report/submit/route.ts), POST /api/vat-report/receipt (henter kvittering efter godkendelse, src/app/api/vat-report/receipt/route.ts) og GET /api/vat-report/submissions (historik, src/app/api/vat-report/submissions/route.ts). Alle API'er er sikret med relevante rettigheder, blokerer oversight- og demo-miljøer og kræver TokenPay-adgang.
 Arkitektur: AlphaFlow forbinder til SKATs RSU B2B gateway via SOAP/XML over HTTPS med mutual TLS (mTLS) og WS-Security XML-signatur — ikke OAuth2/REST. Integrationen implementerer de tre officielle SOAP-webservices fra Skattestyrelsen: (1) VirksomhedKalenderHent — henter momsperioder og frister for et SE-nummer; (2) ModtagMomsangivelseForeloebig — indsender en foreløbig momsangivelse (udkast) med de 17 momsbeløbsfelter; (3) MomsangivelseKvitteringHent — henter kvittering (PDF) efter brugeren har godkendt i TastSelv Erhverv. Klienten er implementeret i src/lib/skat-soap-client.ts med SOAP-envelope-byggere for alle tre servicer, de 17 momsangivelse-feltnavne i korrekt XSD-sekvens, respons-parsere og mapping af AlphaFlows momsregister til de 17 SKAT-felter (felt 14: salgsmoms, felt 9: købsmoms, felt 1: afgiftstilsvar).
 Autentificering: Mutual TLS med VOCES3 System (S1) certifikat fra MitID Erhverv samt WS-Security XML-signatur over Timestamp og Body. Onboarding: AlphaFlow har ansøgt Skattestyrelsen om test-endpoints og test VOCES3-certifikat; hver kundevirksomhed skal delegere "Nemvirksomhed – adgang for systemudbyder" til AlphaFlows CVR på skat.dk (engang pr. kunde).
 Flow: (1) AlphaFlow indsender et udkast via ModtagMomsangivelseForeloebig → returnerer transaktionsidentifikator og dybtlink (deep URL til TastSelv Erhverv); (2) brugeren klikker dybtlinket, logger ind med MitID og godkender de præ-udfyldte tal; (3) AlphaFlow henter kvittering via MomsangivelseKvitteringHent med transaktionsidentifikator — returnerer PDF-kvittering og betalingsinfo. Hvis brugeren endnu ikke har godkendt, returneres fejlkode 4810. Fejlkode 5001 = ordinær angivelse, 5002 = efterangivelse.

--- a/docs/SvarPåAnmodningForZ_updated.xlsx
+++ b/docs/SvarPåAnmodningForZ_updated.xlsx
@@ -4869,7 +4869,7 @@
 7. Journalposter og linjer oprettes med automatisk momskode-mapping via tre strategier: (1) StandardTaxCode reverse lookup via src/lib/saft-vat-codes.ts, (2) momssats-heuristik (25%/12%/0% × salg/køb), (3) direkte match med AlphaFlow interne koder
 8. Bilagsnumre tildeles via AlphaFlow's egen sekvens (ikke kilde-systemets) for at overholde Bogføringsloven §14
 9. Audit-log for hele importen
-(b) AlphaFlow tenant-snapshot import: Et AlphaFlow-specifikt portabelt format (manifest.json + JSON-filer) via /api/import-tenant (src/app/api/import-tenant/route.ts), som genopretter alle 14 entiteter inklusive bilagsfiler. Designet til udbyderskift fra AlphaFlow eller kompatible systemer.
+(b) AlphaFlow tenant-snapshot import: Et portabelt format (manifest.json + JSON-filer) via /api/import-tenant (src/app/api/import-tenant/route.ts), som genopretter alle 14 entiteter inklusive bilagsfiler. Designet til udbyderskift fra AlphaFlow eller kompatible systemer.
 Teknisk dokumentation: Parser: src/lib/saft-import/parser.ts (XML → JS objekter via fast-xml-parser), Transformer: src/lib/saft-import/transformer.ts (SAF-T typer → Prisma modeller + VAT mapping), AccountGroup-afledning: src/lib/saft-import/account-group-inference.ts, Landekode-mapping: src/lib/saft-import/country-codes.ts.
 Kravet er fuldt opfyldt — AlphaFlow kan indlæse SAF-T XML-standardfiler fra vilkårlige tredjepartssystemer.</t>
         </is>

--- a/docs/SvarPåAnmodningForZ_updated.xlsx
+++ b/docs/SvarPåAnmodningForZ_updated.xlsx
@@ -5244,7 +5244,7 @@
         </is>
       </c>
     </row>
-    <row r="456" ht="395.65" customHeight="1" s="18">
+    <row r="456" ht="685" customHeight="1" s="18">
       <c r="A456" s="1" t="inlineStr">
         <is>
           <t>Udbyderens bemærkninger</t>
@@ -5252,12 +5252,28 @@
       </c>
       <c r="B456" s="20" t="inlineStr">
         <is>
-          <t>Kravet er fuldt opfyldt. AlphaFlow opfylder kravet via en fuldendt samtykkestyret tilmeldingsflow.
-(1) Kunden informeres: via in-app banner (nemhandel-registration-notice.tsx) eller e-mail-notifikation (Række 47-mekanismen), begge med dybtlink til /settings-edelivery.
-(2) Kunden navigerer: Sidekomponenten EInvoiceSettingsPage (einvoice-settings-page.tsx) viser banneret samt EInvoiceSettings-komponenten (src/components/settings/einvoice-settings.tsx), hvor kunden vælger leveringsmåde.
-(3) Kunden markerer samtykke og giver accept: Kunden vælger "automatisk" leveringsmåde, hvorefter systemet opdaterer virksomhedens indstilling via API'et /api/company/einvoice. Samtykket er udtrykkeligt — kunden skal aktivt vælge leveringsmåde for at aktivere e-faktura.
-(4) Bekræftelse: Systemet bekræfter tilmeldingen i brugergrænsefladen og fjerner banneret. Kunden kan til enhver tid ændre eller deaktivere leveringsmåde via samme indstillingsside.
-Teknisk dokumentation findes i src/components/settings/nemhandel-registration-notice.tsx, src/components/settings/einvoice-settings-page.tsx, src/components/settings/einvoice-settings.tsx og src/app/api/company/einvoice/route.ts.</t>
+          <t>KRAVET ER FULDT OPFYLDT.
+VIGTIGT OM ACCESS POINT: Udbyderbeskrivelsen ovenfor nævner Storecove som Access Point. AlphaFlow har skiftet til Sproom — den aktuelle produktionintegration er derfor Sproom, ikke Storecove. Sproom håndterer Peppol/NemHandel som AlphaFlows Access Point i produktion.
+AlphaFlow opfylder kravet gennem et samtykkestyret tilmeldingsflow i fem trin:
+TRIN 1 — Kunden informeres
+Via in-app banner (nemhandel-registration-notice.tsx) eller e-mail-notifikation (Række 47-mekanismen), begge med dybtlink til /settings-edelivery.
+TRIN 2 — Kunden navigerer til tilmeldingssiden
+Sidekomponenten EInvoiceSettingsPage (einvoice-settings-page.tsx) renderer banneret + EInvoiceSettings-komponenten (src/components/settings/einvoice-settings.tsx), hvor kunden vælger leveringsmåde.
+TRIN 3 — Kunden markerer samtykke og giver accept
+• Kunden vælger "automatic" leveringsmåde. PUT /api/company/einvoice-settings (src/app/api/company/einvoice-settings/route.ts linje 67-97) validerer, at EndpointID er påkrævet og har formatet scheme:identifier (f.eks. 0184:12345678 for DK CVR).
+• Kunden opretter en Sproom child company — AlphaFlows Access Point (se getActiveAccessPoint() i src/lib/einvoice-sender.ts linje 58-60, som returnerer 'sproom' når Sproom er konfigureret).
+• Når Sproom er forbundet, aktiveres knappen "Tilmeld NemHandelsregisteret" (einvoice-settings.tsx linje 1051-1066; disabled når nemhandelLoading || !companyCvr || !sproomStatus?.connected).
+• Klik på knappen er kundens udtrykkelige samtykke og kalder handleNemHandelRegister (einvoice-settings.tsx linje 545-581), som POSTer til /api/sproom/register-nemhandel.
+TRIN 4 — AlphaFlow håndterer tilmeldingen
+Routen src/app/api/sproom/register-nemhandel/route.ts:
+• Validerer preconditions (child company eksisterer, CVR sat, Sproom konfigureret).
+• Kontrollerer idempotency (Company.sproomNemHandelRegistered allerede true → returnerer succes uden re-kald).
+• Kalder sproomClient.registerNemHandel({schemeId: 'DK:CVR', value: cvr}, ['Nes5Customer'], {childCompanyId}) (src/lib/sproom-client.ts linje 1437-1472), som POSTer til Sproom-API'et /api/registrations/nemhandel.
+• Ved succes persisteres Company.sproomNemHandelRegistered = true + sproomLastTestedAt = now (linje 109-115), og AuditLog-entry sproom_nemhandel_registered skrives (linje 124-135).
+TRIN 5 — Standardfunktioner håndteres af Sproom
+Sproom håndterer automatisk NemHandel eDelivery-overensstemmelse: MitID Erhverv-certifikat, OIOUBL 2.1 schema- og schematron-validering, MLR/AR-returnering.
+BEMÆRKNING OM LEGACY-KODE: En ældre funktion registerNemHandel i einvoice-sender.ts (kaldt af /api/company/einvoice-register) kører i simulation mode (simulationMode: true, linje 134) og er dokumenteret som "Currently simulated — in production, registration is handled through the NHR portal or via Sproom onboarding" (linje 1559-1560). Sproom er således den eneste produktion Access Point.
+Dokumenteret i Bilag 6 afsnit 16.3 + 16.11. Skærmbilleder vil blive fremsendt.</t>
         </is>
       </c>
     </row>

--- a/docs/SvarPåAnmodningForZ_updated.xlsx
+++ b/docs/SvarPåAnmodningForZ_updated.xlsx
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Tenant-import + restore fra backup-ZIP.</t>
+          <t>SAF-T XML-import (indlæsning af standardfil) + tenant-import + restore fra backup-ZIP.</t>
         </is>
       </c>
     </row>
@@ -4856,22 +4856,24 @@
       <c r="B420" s="20" t="inlineStr">
         <is>
           <t>Kravet er opfyldt. AlphaFlow understøtter to importmetoder til overførsel af data fra et andet bogføringssystem:
-(a) SAF-T XML-import (ny): AlphaFlow kan importere en SAF-T Financial DK v2.1 XML-fil fra et vilkårligt tredjepartssystem (f.eks. e-conomic, Dinero, Visma) via API'et /api/import-saft (src/app/api/import-saft/route.ts). API'en er sikret med rettigheder til backup/gendannelse, blokerer oversight- og demo-miljøer, kræver TokenPay-adgang og accepterer en XML-fil (maks. 100 MB).
+(a) SAF-T XML-import (standardfil): AlphaFlow kan importere en SAF-T Financial DK v2.1 XML-fil fra et vilkårligt tredjepartssystem (f.eks. e-conomic, Dinero, Visma) via API'et /api/import-saft (src/app/api/import-saft/route.ts). API'en er sikret med rettigheder til backup/gendannelse (Permission.BACKUP_RESTORE, min. rolle OWNER), blokerer oversight- og demo-miljøer, kræver TokenPay-adgang og accepterer en XML-fil (maks. 100 MB).
+§10-12 COMPLIANCE (Bogføringsloven): Import sletter al eksisterende tenant-data og genskaber dem fra SAF-T-filen. Fordi bogførte posteringer er uforanderlige jf. Bogføringsloven §10-12 ("bogførte transaktioner ikke kan ændres, tilbagedateres eller slettes"), er importen KUN tilladt som en førstegangs overflytning i en tenant uden bogførte data. Bevogtningen implementeres i src/lib/tenant-import-guard.ts (getTenantPopulation()), som tæller eksisterende POSTED journalposter, forsegilede transaktioner (recordHash IS NOT NULL) og lukkede regnskabsperioder (status = 'CLOSED'). Findes der blot én sådan post, afvises importen med HTTP 409 (TENANT_ALREADY_POPULATED) — FØR immutability-bypassen aktiveres — så database-triggerne i prisma/journal-immutability.sql forbliver fuldt aktive, og eksisterende bogført data ikke kan overskrives. DRAFT-journalposter (uden recordHash) er ikke omfattet af §10-12 og må slettes. Det blokerede forsøg logges uforanderligt i AuditLog som DELETE_ATTEMPT.
 Importen foregår i to trin:
-Trin 1 — Pre-flight (dry-run): Før importen kan brugeren validere filen via /api/import-saft/dry-run (src/app/api/import-saft/dry-run/route.ts), som parser XML'en, tjekker for konflikter med eksisterende konti, identificerer umappede momskoder og returnerer et summary med antal konti, kunder, leverandører, posteringer og linjer — uden at ændre nogen data. Brugeren kan reviewe konflikter og advarsler før importen bekræftes.
-Trin 2 — Import: Når brugeren bekræfter, udføres importen i én samlet database-transaktion med følgende trin:
-1. Eksisterende virksomhedsdata slettes (respekterer FK-afhængigheder)
-2. Bogføringslovens immutability-triggere bypasses sikkert (SET LOCAL app.immutability_bypass = 'true')
-3. Virksomhedsoplysninger opdateres fra SAF-T Header
-4. Konti oprettes med automatisk AccountGroup-afledning (src/lib/saft-import/account-group-inference.ts) — afleder gruppe fra StandardAccountID og kontonummer-række
-5. Kontakter oprettes med automatisk landekode-konvertering (src/lib/saft-import/country-codes.ts) — ISO 3166-1 alpha-2 → dansk navn
-6. Regnskabsperioder oprettes baseret på posteringernes periode-data
-7. Journalposter og linjer oprettes med automatisk momskode-mapping via tre strategier: (1) StandardTaxCode reverse lookup via src/lib/saft-vat-codes.ts, (2) momssats-heuristik (25%/12%/0% × salg/køb), (3) direkte match med AlphaFlow interne koder
-8. Bilagsnumre tildeles via AlphaFlow's egen sekvens (ikke kilde-systemets) for at overholde Bogføringsloven §14
-9. Audit-log for hele importen
+Trin 1 — Pre-flight (dry-run): Før importen kan brugeren validere filen via /api/import-saft/dry-run (src/app/api/import-saft/dry-run/route.ts), som parser XML'en, tjekker for konflikter med eksisterende konti, identificerer umappede momskoder, returnerer tenantens befolkningstilstand (populatedTenant) og et summary med antal konti, kunder, leverandører, posteringer og linjer — uden at ændre nogen data. Frontend (src/components/exports/saft-import-section.tsx) deaktiverer knappen "Bekræft import" og viser en rød §10-12-advarsel, hvis tenanten allerede indeholder bogførte data.
+Trin 2 — Import: Når brugeren bekræfter (kun muligt i en ubefolket tenant), udføres importen i én samlet database-transaktion med følgende trin:
+1. §10-12-guard konsulteres (getTenantPopulation) — importen afvises, hvis tenanten har bogførte data
+2. Bogføringslovens immutability-triggere bypasses KUN for denne one-time operation (SET LOCAL app.immutability_bypass = 'true') — sikkert, fordi guarden bekræftede, at der ikke er bogført data at overskrive
+3. Eksisterende kladder/data slettes (respekterer FK-afhængigheder)
+4. Virksomhedsoplysninger opdateres fra SAF-T Header
+5. Konti oprettes med automatisk AccountGroup-afledning (src/lib/saft-import/account-group-inference.ts) — afleder gruppe fra StandardAccountID og kontonummer-række
+6. Kontakter oprettes med automatisk landekode-konvertering (src/lib/saft-import/country-codes.ts) — ISO 3166-1 alpha-2 → dansk navn
+7. Regnskabsperioder oprettes baseret på posteringernes periode-data
+8. Journalposter og linjer oprettes med automatisk momskode-mapping via tre strategier: (1) StandardTaxCode reverse lookup via src/lib/saft-vat-codes.ts, (2) momssats-heuristik (25%/12%/0% × salg/køb), (3) direkte match med AlphaFlow interne koder
+9. Bilagsnumre tildeles via AlphaFlow's egen sekvens (ikke kilde-systemets) for at overholde Bogføringsloven §14
+10. Audit-log for hele importen
 (b) AlphaFlow tenant-snapshot import: Et portabelt format (manifest.json + JSON-filer) via /api/import-tenant (src/app/api/import-tenant/route.ts), som genopretter alle 14 entiteter inklusive bilagsfiler. Designet til udbyderskift fra AlphaFlow eller kompatible systemer.
-Teknisk dokumentation: Parser: src/lib/saft-import/parser.ts (XML → JS objekter via fast-xml-parser), Transformer: src/lib/saft-import/transformer.ts (SAF-T typer → Prisma modeller + VAT mapping), AccountGroup-afledning: src/lib/saft-import/account-group-inference.ts, Landekode-mapping: src/lib/saft-import/country-codes.ts.
-Kravet er fuldt opfyldt — AlphaFlow kan indlæse SAF-T XML-standardfiler fra vilkårlige tredjepartssystemer.</t>
+Teknisk dokumentation: Parser: src/lib/saft-import/parser.ts (XML → JS objekter via fast-xml-parser), Transformer: src/lib/saft-import/transformer.ts (SAF-T typer → Prisma modeller + VAT mapping), AccountGroup-afledning: src/lib/saft-import/account-group-inference.ts, Landekode-mapping: src/lib/saft-import/country-codes.ts, §10-12-guard: src/lib/tenant-import-guard.ts.
+Kravet er fuldt opfyldt — AlphaFlow kan indlæse SAF-T XML-standardfiler fra vilkårlige tredjepartssystemer, og Bogføringsloven §10-12 overholdes: import kan kun gennemføres i en tenant uden bogførte data, så eksisterende bogført data kan ikke overskrives.</t>
         </is>
       </c>
     </row>
